--- a/test/P5/P5_Jitter&Eye.xlsx
+++ b/test/P5/P5_Jitter&Eye.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FK\script\Soft\test\P5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\Scripts\TEST_P5\test\P5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD04AA1-3CAF-42EB-93A9-59FD6B8CCEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5CF33-D6AB-4DA4-BC36-85411DB303AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="24">
   <si>
     <t>chipnum</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>prbs31</t>
+  </si>
+  <si>
+    <t>FF01</t>
   </si>
 </sst>
 </file>
@@ -430,14 +433,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q45"/>
-  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q89"/>
+  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="6" width="9.08203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.08203125" style="1"/>
+    <col min="1" max="7" width="9.06640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -490,7 +493,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -543,7 +546,7 @@
         <v>0.318</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -596,7 +599,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -649,7 +652,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -702,7 +705,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -755,7 +758,7 @@
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -808,7 +811,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -861,7 +864,7 @@
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -914,7 +917,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -967,7 +970,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1020,7 +1023,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -1073,7 +1076,7 @@
         <v>0.127</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -1126,7 +1129,7 @@
         <v>0.11700000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,7 +1182,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -1285,7 +1288,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -1338,7 +1341,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,7 +1394,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1444,7 +1447,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -1497,7 +1500,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1550,7 +1553,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1656,7 +1659,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -1709,7 +1712,7 @@
         <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>17</v>
       </c>
@@ -1762,7 +1765,7 @@
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>17</v>
       </c>
@@ -1815,7 +1818,7 @@
         <v>0.20599999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>17</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>0.158</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
@@ -1921,7 +1924,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>17</v>
       </c>
@@ -1974,7 +1977,7 @@
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>17</v>
       </c>
@@ -2027,7 +2030,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>17</v>
       </c>
@@ -2080,7 +2083,7 @@
         <v>0.17599999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>17</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
@@ -2186,7 +2189,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>17</v>
       </c>
@@ -2239,7 +2242,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>17</v>
       </c>
@@ -2292,7 +2295,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>17</v>
       </c>
@@ -2345,7 +2348,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2398,7 +2401,7 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>17</v>
       </c>
@@ -2451,7 +2454,7 @@
         <v>0.155</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>17</v>
       </c>
@@ -2504,7 +2507,7 @@
         <v>0.16400000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>17</v>
       </c>
@@ -2557,7 +2560,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
@@ -2610,7 +2613,7 @@
         <v>0.13800000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>17</v>
       </c>
@@ -2663,7 +2666,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>17</v>
       </c>
@@ -2716,7 +2719,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>17</v>
       </c>
@@ -2769,7 +2772,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>17</v>
       </c>
@@ -2820,11 +2823,2343 @@
       </c>
       <c r="Q45" s="1">
         <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46">
+        <v>32</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46">
+        <v>24</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>682.2</v>
+      </c>
+      <c r="J46">
+        <v>558.73</v>
+      </c>
+      <c r="K46">
+        <v>29.645</v>
+      </c>
+      <c r="L46">
+        <v>4.2990000000000004</v>
+      </c>
+      <c r="M46">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="N46">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="O46">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47">
+        <v>32</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>24</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>1263</v>
+      </c>
+      <c r="J47">
+        <v>262</v>
+      </c>
+      <c r="K47">
+        <v>26.010999999999999</v>
+      </c>
+      <c r="L47">
+        <v>11.404</v>
+      </c>
+      <c r="M47">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="N47">
+        <v>4.4489999999999998</v>
+      </c>
+      <c r="O47">
+        <v>1.008</v>
+      </c>
+      <c r="P47">
+        <v>4.1609999999999996</v>
+      </c>
+      <c r="Q47">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48">
+        <v>32</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48">
+        <v>24</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48">
+        <v>1233</v>
+      </c>
+      <c r="J48">
+        <v>290.89999999999998</v>
+      </c>
+      <c r="K48">
+        <v>26.809000000000001</v>
+      </c>
+      <c r="L48">
+        <v>11.131</v>
+      </c>
+      <c r="M48">
+        <v>0.498</v>
+      </c>
+      <c r="N48">
+        <v>4.125</v>
+      </c>
+      <c r="O48">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="P48">
+        <v>3.9420000000000002</v>
+      </c>
+      <c r="Q48">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49">
+        <v>32</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49">
+        <v>24</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+      <c r="I49">
+        <v>1172</v>
+      </c>
+      <c r="J49">
+        <v>321</v>
+      </c>
+      <c r="K49">
+        <v>26.754999999999999</v>
+      </c>
+      <c r="L49">
+        <v>10.563000000000001</v>
+      </c>
+      <c r="M49">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="N49">
+        <v>3.78</v>
+      </c>
+      <c r="O49">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="P49">
+        <v>3.6480000000000001</v>
+      </c>
+      <c r="Q49">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50">
+        <v>32</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50">
+        <v>24</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>6</v>
+      </c>
+      <c r="I50">
+        <v>1125</v>
+      </c>
+      <c r="J50">
+        <v>348</v>
+      </c>
+      <c r="K50">
+        <v>26.96</v>
+      </c>
+      <c r="L50">
+        <v>9.8840000000000003</v>
+      </c>
+      <c r="M50">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="N50">
+        <v>3.4510000000000001</v>
+      </c>
+      <c r="O50">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="P50">
+        <v>3.4249999999999998</v>
+      </c>
+      <c r="Q50">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51">
+        <v>32</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51">
+        <v>24</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>8</v>
+      </c>
+      <c r="I51">
+        <v>1083</v>
+      </c>
+      <c r="J51">
+        <v>378.5</v>
+      </c>
+      <c r="K51">
+        <v>27.536999999999999</v>
+      </c>
+      <c r="L51">
+        <v>9.6630000000000003</v>
+      </c>
+      <c r="M51">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="N51">
+        <v>3.1760000000000002</v>
+      </c>
+      <c r="O51">
+        <v>0.876</v>
+      </c>
+      <c r="P51">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="Q51">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52">
+        <v>32</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52">
+        <v>24</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>10</v>
+      </c>
+      <c r="I52">
+        <v>1039</v>
+      </c>
+      <c r="J52">
+        <v>403.5</v>
+      </c>
+      <c r="K52">
+        <v>27.401</v>
+      </c>
+      <c r="L52">
+        <v>9.3040000000000003</v>
+      </c>
+      <c r="M52">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="N52">
+        <v>2.7930000000000001</v>
+      </c>
+      <c r="O52">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="P52">
+        <v>2.7909999999999999</v>
+      </c>
+      <c r="Q52">
+        <v>7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53">
+        <v>32</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53">
+        <v>24</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>12</v>
+      </c>
+      <c r="I53">
+        <v>994</v>
+      </c>
+      <c r="J53">
+        <v>436</v>
+      </c>
+      <c r="K53">
+        <v>27.742000000000001</v>
+      </c>
+      <c r="L53">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="M53">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="N53">
+        <v>2.5289999999999999</v>
+      </c>
+      <c r="O53">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="P53">
+        <v>2.5</v>
+      </c>
+      <c r="Q53">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54">
+        <v>32</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54">
+        <v>24</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>14</v>
+      </c>
+      <c r="I54">
+        <v>952</v>
+      </c>
+      <c r="J54">
+        <v>457.2</v>
+      </c>
+      <c r="K54">
+        <v>27.681000000000001</v>
+      </c>
+      <c r="L54">
+        <v>8.4870000000000001</v>
+      </c>
+      <c r="M54">
+        <v>0.43</v>
+      </c>
+      <c r="N54">
+        <v>2.431</v>
+      </c>
+      <c r="O54">
+        <v>0.76</v>
+      </c>
+      <c r="P54">
+        <v>2.4860000000000002</v>
+      </c>
+      <c r="Q54">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55">
+        <v>32</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55">
+        <v>24</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>16</v>
+      </c>
+      <c r="I55">
+        <v>898</v>
+      </c>
+      <c r="J55">
+        <v>476</v>
+      </c>
+      <c r="K55">
+        <v>27.548999999999999</v>
+      </c>
+      <c r="L55">
+        <v>8.7119999999999997</v>
+      </c>
+      <c r="M55">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="N55">
+        <v>2.7810000000000001</v>
+      </c>
+      <c r="O55">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="P55">
+        <v>2.5430000000000001</v>
+      </c>
+      <c r="Q55">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56">
+        <v>32</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56">
+        <v>24</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>18</v>
+      </c>
+      <c r="I56">
+        <v>882</v>
+      </c>
+      <c r="J56">
+        <v>483.5</v>
+      </c>
+      <c r="K56">
+        <v>27.547999999999998</v>
+      </c>
+      <c r="L56">
+        <v>8.843</v>
+      </c>
+      <c r="M56">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="N56">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="O56">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="P56">
+        <v>2.8069999999999999</v>
+      </c>
+      <c r="Q56">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>23</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57">
+        <v>32</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57">
+        <v>24</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>20</v>
+      </c>
+      <c r="I57">
+        <v>856</v>
+      </c>
+      <c r="J57">
+        <v>477</v>
+      </c>
+      <c r="K57">
+        <v>27.666</v>
+      </c>
+      <c r="L57">
+        <v>9.0090000000000003</v>
+      </c>
+      <c r="M57">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="N57">
+        <v>3.3279999999999998</v>
+      </c>
+      <c r="O57">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="P57">
+        <v>3.1419999999999999</v>
+      </c>
+      <c r="Q57">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>23</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58">
+        <v>32</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58">
+        <v>24</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>14</v>
+      </c>
+      <c r="I58">
+        <v>951</v>
+      </c>
+      <c r="J58">
+        <v>456.8</v>
+      </c>
+      <c r="K58">
+        <v>27.765000000000001</v>
+      </c>
+      <c r="L58">
+        <v>8.4239999999999995</v>
+      </c>
+      <c r="M58">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="N58">
+        <v>2.3860000000000001</v>
+      </c>
+      <c r="O58">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="P58">
+        <v>2.294</v>
+      </c>
+      <c r="Q58">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59">
+        <v>32</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>20</v>
+      </c>
+      <c r="F59">
+        <v>24</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+      <c r="H59">
+        <v>14</v>
+      </c>
+      <c r="I59">
+        <v>905</v>
+      </c>
+      <c r="J59">
+        <v>460.8</v>
+      </c>
+      <c r="K59">
+        <v>27.475000000000001</v>
+      </c>
+      <c r="L59">
+        <v>8.3149999999999995</v>
+      </c>
+      <c r="M59">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="N59">
+        <v>2.4580000000000002</v>
+      </c>
+      <c r="O59">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="P59">
+        <v>2.29</v>
+      </c>
+      <c r="Q59">
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60">
+        <v>32</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60">
+        <v>24</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60">
+        <v>14</v>
+      </c>
+      <c r="I60">
+        <v>880</v>
+      </c>
+      <c r="J60">
+        <v>454.3</v>
+      </c>
+      <c r="K60">
+        <v>27.274999999999999</v>
+      </c>
+      <c r="L60">
+        <v>8.7449999999999992</v>
+      </c>
+      <c r="M60">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="N60">
+        <v>2.8180000000000001</v>
+      </c>
+      <c r="O60">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="P60">
+        <v>2.597</v>
+      </c>
+      <c r="Q60">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61">
+        <v>32</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61">
+        <v>24</v>
+      </c>
+      <c r="G61">
+        <v>6</v>
+      </c>
+      <c r="H61">
+        <v>14</v>
+      </c>
+      <c r="I61">
+        <v>847</v>
+      </c>
+      <c r="J61">
+        <v>439</v>
+      </c>
+      <c r="K61">
+        <v>26.884</v>
+      </c>
+      <c r="L61">
+        <v>8.8490000000000002</v>
+      </c>
+      <c r="M61">
+        <v>0.378</v>
+      </c>
+      <c r="N61">
+        <v>3.5329999999999999</v>
+      </c>
+      <c r="O61">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="P61">
+        <v>3.2469999999999999</v>
+      </c>
+      <c r="Q61">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62">
+        <v>32</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62">
+        <v>24</v>
+      </c>
+      <c r="G62">
+        <v>8</v>
+      </c>
+      <c r="H62">
+        <v>14</v>
+      </c>
+      <c r="I62">
+        <v>817</v>
+      </c>
+      <c r="J62">
+        <v>405.5</v>
+      </c>
+      <c r="K62">
+        <v>27.071000000000002</v>
+      </c>
+      <c r="L62">
+        <v>9.1059999999999999</v>
+      </c>
+      <c r="M62">
+        <v>0.378</v>
+      </c>
+      <c r="N62">
+        <v>3.7829999999999999</v>
+      </c>
+      <c r="O62">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="P62">
+        <v>3.6120000000000001</v>
+      </c>
+      <c r="Q62">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63">
+        <v>32</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <v>24</v>
+      </c>
+      <c r="G63">
+        <v>10</v>
+      </c>
+      <c r="H63">
+        <v>14</v>
+      </c>
+      <c r="I63">
+        <v>792</v>
+      </c>
+      <c r="J63">
+        <v>364</v>
+      </c>
+      <c r="K63">
+        <v>26.867000000000001</v>
+      </c>
+      <c r="L63">
+        <v>9.3249999999999993</v>
+      </c>
+      <c r="M63">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="N63">
+        <v>4.202</v>
+      </c>
+      <c r="O63">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="P63">
+        <v>4.1059999999999999</v>
+      </c>
+      <c r="Q63">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64">
+        <v>32</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>20</v>
+      </c>
+      <c r="F64">
+        <v>24</v>
+      </c>
+      <c r="G64">
+        <v>12</v>
+      </c>
+      <c r="H64">
+        <v>14</v>
+      </c>
+      <c r="I64">
+        <v>769.5</v>
+      </c>
+      <c r="J64">
+        <v>317.60000000000002</v>
+      </c>
+      <c r="K64">
+        <v>25.56</v>
+      </c>
+      <c r="L64">
+        <v>9.5709999999999997</v>
+      </c>
+      <c r="M64">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="N64">
+        <v>4.7489999999999997</v>
+      </c>
+      <c r="O64">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="P64">
+        <v>4.5380000000000003</v>
+      </c>
+      <c r="Q64">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65">
+        <v>32</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65">
+        <v>24</v>
+      </c>
+      <c r="G65">
+        <v>14</v>
+      </c>
+      <c r="H65">
+        <v>14</v>
+      </c>
+      <c r="I65">
+        <v>749</v>
+      </c>
+      <c r="J65">
+        <v>263</v>
+      </c>
+      <c r="K65">
+        <v>26.628</v>
+      </c>
+      <c r="L65">
+        <v>9.99</v>
+      </c>
+      <c r="M65">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="N65">
+        <v>5.3339999999999996</v>
+      </c>
+      <c r="O65">
+        <v>0.84</v>
+      </c>
+      <c r="P65">
+        <v>5.1719999999999997</v>
+      </c>
+      <c r="Q65">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>23</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66">
+        <v>32</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66">
+        <v>24</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66">
+        <v>14</v>
+      </c>
+      <c r="I66">
+        <v>940</v>
+      </c>
+      <c r="J66">
+        <v>455.8</v>
+      </c>
+      <c r="K66">
+        <v>27.706</v>
+      </c>
+      <c r="L66">
+        <v>9.3089999999999993</v>
+      </c>
+      <c r="M66">
+        <v>0.434</v>
+      </c>
+      <c r="N66">
+        <v>3.2010000000000001</v>
+      </c>
+      <c r="O66">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="P66">
+        <v>3.6789999999999998</v>
+      </c>
+      <c r="Q66">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>23</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67">
+        <v>32</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>22</v>
+      </c>
+      <c r="F67">
+        <v>24</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>14</v>
+      </c>
+      <c r="I67">
+        <v>938</v>
+      </c>
+      <c r="J67">
+        <v>455.6</v>
+      </c>
+      <c r="K67">
+        <v>27.658000000000001</v>
+      </c>
+      <c r="L67">
+        <v>9.3770000000000007</v>
+      </c>
+      <c r="M67">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="N67">
+        <v>2.2570000000000001</v>
+      </c>
+      <c r="O67">
+        <v>0.73</v>
+      </c>
+      <c r="P67">
+        <v>2.379</v>
+      </c>
+      <c r="Q67">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68">
+        <v>16</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68">
+        <v>24</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>1006</v>
+      </c>
+      <c r="J68">
+        <v>765.1</v>
+      </c>
+      <c r="K68">
+        <v>60.393999999999998</v>
+      </c>
+      <c r="L68">
+        <v>5.8360000000000003</v>
+      </c>
+      <c r="M68">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="N68">
+        <v>0.217</v>
+      </c>
+      <c r="O68">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69">
+        <v>16</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69">
+        <v>24</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>1335</v>
+      </c>
+      <c r="J69">
+        <v>592</v>
+      </c>
+      <c r="K69">
+        <v>57.552</v>
+      </c>
+      <c r="L69">
+        <v>9.7669999999999995</v>
+      </c>
+      <c r="M69">
+        <v>0.497</v>
+      </c>
+      <c r="N69">
+        <v>2.7669999999999999</v>
+      </c>
+      <c r="O69">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="P69">
+        <v>2.9409999999999998</v>
+      </c>
+      <c r="Q69">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70">
+        <v>16</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70">
+        <v>24</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>2</v>
+      </c>
+      <c r="I70">
+        <v>1289</v>
+      </c>
+      <c r="J70">
+        <v>623.20000000000005</v>
+      </c>
+      <c r="K70">
+        <v>57.985999999999997</v>
+      </c>
+      <c r="L70">
+        <v>9.5039999999999996</v>
+      </c>
+      <c r="M70">
+        <v>0.504</v>
+      </c>
+      <c r="N70">
+        <v>2.4049999999999998</v>
+      </c>
+      <c r="O70">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="P70">
+        <v>2.5550000000000002</v>
+      </c>
+      <c r="Q70">
+        <v>0.14099999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71">
+        <v>16</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71">
+        <v>24</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>4</v>
+      </c>
+      <c r="I71">
+        <v>1254</v>
+      </c>
+      <c r="J71">
+        <v>651.20000000000005</v>
+      </c>
+      <c r="K71">
+        <v>58.484999999999999</v>
+      </c>
+      <c r="L71">
+        <v>9.0850000000000009</v>
+      </c>
+      <c r="M71">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="N71">
+        <v>2.2530000000000001</v>
+      </c>
+      <c r="O71">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="P71">
+        <v>2.4489999999999998</v>
+      </c>
+      <c r="Q71">
+        <v>0.14299999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>23</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72">
+        <v>16</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72">
+        <v>24</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>6</v>
+      </c>
+      <c r="I72">
+        <v>1213</v>
+      </c>
+      <c r="J72">
+        <v>678</v>
+      </c>
+      <c r="K72">
+        <v>58.872999999999998</v>
+      </c>
+      <c r="L72">
+        <v>9.0220000000000002</v>
+      </c>
+      <c r="M72">
+        <v>0.497</v>
+      </c>
+      <c r="N72">
+        <v>2.0350000000000001</v>
+      </c>
+      <c r="O72">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="P72">
+        <v>2.2970000000000002</v>
+      </c>
+      <c r="Q72">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73">
+        <v>16</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73">
+        <v>24</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>8</v>
+      </c>
+      <c r="I73">
+        <v>1154</v>
+      </c>
+      <c r="J73">
+        <v>702.4</v>
+      </c>
+      <c r="K73">
+        <v>59.162999999999997</v>
+      </c>
+      <c r="L73">
+        <v>8.7509999999999994</v>
+      </c>
+      <c r="M73">
+        <v>0.497</v>
+      </c>
+      <c r="N73">
+        <v>1.758</v>
+      </c>
+      <c r="O73">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="P73">
+        <v>2.0270000000000001</v>
+      </c>
+      <c r="Q73">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74">
+        <v>16</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74" t="s">
+        <v>20</v>
+      </c>
+      <c r="F74">
+        <v>24</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>10</v>
+      </c>
+      <c r="I74">
+        <v>1129</v>
+      </c>
+      <c r="J74">
+        <v>716.8</v>
+      </c>
+      <c r="K74">
+        <v>59.351999999999997</v>
+      </c>
+      <c r="L74">
+        <v>8.577</v>
+      </c>
+      <c r="M74">
+        <v>0.498</v>
+      </c>
+      <c r="N74">
+        <v>1.5720000000000001</v>
+      </c>
+      <c r="O74">
+        <v>0.62</v>
+      </c>
+      <c r="P74">
+        <v>1.835</v>
+      </c>
+      <c r="Q74">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75">
+        <v>16</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75">
+        <v>24</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>12</v>
+      </c>
+      <c r="I75">
+        <v>1073</v>
+      </c>
+      <c r="J75">
+        <v>718.4</v>
+      </c>
+      <c r="K75">
+        <v>59.543999999999997</v>
+      </c>
+      <c r="L75">
+        <v>8.1769999999999996</v>
+      </c>
+      <c r="M75">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="N75">
+        <v>1.36</v>
+      </c>
+      <c r="O75">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="P75">
+        <v>1.7430000000000001</v>
+      </c>
+      <c r="Q75">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>23</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76">
+        <v>16</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76">
+        <v>24</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>14</v>
+      </c>
+      <c r="I76">
+        <v>1093</v>
+      </c>
+      <c r="J76">
+        <v>692.3</v>
+      </c>
+      <c r="K76">
+        <v>59.603000000000002</v>
+      </c>
+      <c r="L76">
+        <v>8.4339999999999993</v>
+      </c>
+      <c r="M76">
+        <v>0.505</v>
+      </c>
+      <c r="N76">
+        <v>1.333</v>
+      </c>
+      <c r="O76">
+        <v>0.59</v>
+      </c>
+      <c r="P76">
+        <v>1.8149999999999999</v>
+      </c>
+      <c r="Q76">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>23</v>
+      </c>
+      <c r="B77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77">
+        <v>16</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77">
+        <v>24</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>16</v>
+      </c>
+      <c r="I77">
+        <v>1069</v>
+      </c>
+      <c r="J77">
+        <v>643.5</v>
+      </c>
+      <c r="K77">
+        <v>59.581000000000003</v>
+      </c>
+      <c r="L77">
+        <v>8.4489999999999998</v>
+      </c>
+      <c r="M77">
+        <v>0.49</v>
+      </c>
+      <c r="N77">
+        <v>1.5489999999999999</v>
+      </c>
+      <c r="O77">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="P77">
+        <v>1.8520000000000001</v>
+      </c>
+      <c r="Q77">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78">
+        <v>16</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78">
+        <v>24</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>18</v>
+      </c>
+      <c r="I78">
+        <v>1065</v>
+      </c>
+      <c r="J78">
+        <v>584.70000000000005</v>
+      </c>
+      <c r="K78">
+        <v>59.125</v>
+      </c>
+      <c r="L78">
+        <v>8.907</v>
+      </c>
+      <c r="M78">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="N78">
+        <v>1.764</v>
+      </c>
+      <c r="O78">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="P78">
+        <v>1.8169999999999999</v>
+      </c>
+      <c r="Q78">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>23</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79">
+        <v>16</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79">
+        <v>24</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>20</v>
+      </c>
+      <c r="I79">
+        <v>1075</v>
+      </c>
+      <c r="J79">
+        <v>509.3</v>
+      </c>
+      <c r="K79">
+        <v>58.555</v>
+      </c>
+      <c r="L79">
+        <v>9.3960000000000008</v>
+      </c>
+      <c r="M79">
+        <v>0.504</v>
+      </c>
+      <c r="N79">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O79">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="P79">
+        <v>2.4169999999999998</v>
+      </c>
+      <c r="Q79">
+        <v>5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>23</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80">
+        <v>16</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80">
+        <v>24</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>12</v>
+      </c>
+      <c r="I80">
+        <v>1083</v>
+      </c>
+      <c r="J80">
+        <v>716</v>
+      </c>
+      <c r="K80">
+        <v>59.521999999999998</v>
+      </c>
+      <c r="L80">
+        <v>8.3970000000000002</v>
+      </c>
+      <c r="M80">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="N80">
+        <v>1.2669999999999999</v>
+      </c>
+      <c r="O80">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="P80">
+        <v>1.7589999999999999</v>
+      </c>
+      <c r="Q80">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>23</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81">
+        <v>16</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81">
+        <v>24</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>12</v>
+      </c>
+      <c r="I81">
+        <v>1043</v>
+      </c>
+      <c r="J81">
+        <v>690.5</v>
+      </c>
+      <c r="K81">
+        <v>59.442999999999998</v>
+      </c>
+      <c r="L81">
+        <v>8.5129999999999999</v>
+      </c>
+      <c r="M81">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="N81">
+        <v>1.59</v>
+      </c>
+      <c r="O81">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="P81">
+        <v>2.1070000000000002</v>
+      </c>
+      <c r="Q81">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>23</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82">
+        <v>16</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82">
+        <v>24</v>
+      </c>
+      <c r="G82">
+        <v>4</v>
+      </c>
+      <c r="H82">
+        <v>12</v>
+      </c>
+      <c r="I82">
+        <v>1031</v>
+      </c>
+      <c r="J82">
+        <v>643.20000000000005</v>
+      </c>
+      <c r="K82">
+        <v>59.411000000000001</v>
+      </c>
+      <c r="L82">
+        <v>8.7210000000000001</v>
+      </c>
+      <c r="M82">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="N82">
+        <v>2.0880000000000001</v>
+      </c>
+      <c r="O82">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="P82">
+        <v>2.4260000000000002</v>
+      </c>
+      <c r="Q82">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83">
+        <v>16</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83">
+        <v>24</v>
+      </c>
+      <c r="G83">
+        <v>6</v>
+      </c>
+      <c r="H83">
+        <v>12</v>
+      </c>
+      <c r="I83">
+        <v>1033</v>
+      </c>
+      <c r="J83">
+        <v>587.1</v>
+      </c>
+      <c r="K83">
+        <v>59.008000000000003</v>
+      </c>
+      <c r="L83">
+        <v>9.0150000000000006</v>
+      </c>
+      <c r="M83">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="N83">
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="O83">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="P83">
+        <v>2.714</v>
+      </c>
+      <c r="Q83">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>23</v>
+      </c>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84">
+        <v>16</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84">
+        <v>24</v>
+      </c>
+      <c r="G84">
+        <v>8</v>
+      </c>
+      <c r="H84">
+        <v>12</v>
+      </c>
+      <c r="I84">
+        <v>1023</v>
+      </c>
+      <c r="J84">
+        <v>513.79999999999995</v>
+      </c>
+      <c r="K84">
+        <v>58.210999999999999</v>
+      </c>
+      <c r="L84">
+        <v>10.036</v>
+      </c>
+      <c r="M84">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="N84">
+        <v>2.3330000000000002</v>
+      </c>
+      <c r="O84">
+        <v>0.182</v>
+      </c>
+      <c r="P84">
+        <v>3.2440000000000002</v>
+      </c>
+      <c r="Q84">
+        <v>8.8999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>23</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85">
+        <v>16</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85">
+        <v>24</v>
+      </c>
+      <c r="G85">
+        <v>10</v>
+      </c>
+      <c r="H85">
+        <v>12</v>
+      </c>
+      <c r="I85">
+        <v>1012</v>
+      </c>
+      <c r="J85">
+        <v>449.3</v>
+      </c>
+      <c r="K85">
+        <v>57.231999999999999</v>
+      </c>
+      <c r="L85">
+        <v>9.8989999999999991</v>
+      </c>
+      <c r="M85">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="N85">
+        <v>3.27</v>
+      </c>
+      <c r="O85">
+        <v>0.627</v>
+      </c>
+      <c r="P85">
+        <v>3.7480000000000002</v>
+      </c>
+      <c r="Q85">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>23</v>
+      </c>
+      <c r="B86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86">
+        <v>16</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86" t="s">
+        <v>20</v>
+      </c>
+      <c r="F86">
+        <v>24</v>
+      </c>
+      <c r="G86">
+        <v>12</v>
+      </c>
+      <c r="H86">
+        <v>12</v>
+      </c>
+      <c r="I86">
+        <v>998</v>
+      </c>
+      <c r="J86">
+        <v>370</v>
+      </c>
+      <c r="K86">
+        <v>56.279000000000003</v>
+      </c>
+      <c r="L86">
+        <v>10.335000000000001</v>
+      </c>
+      <c r="M86">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="N86">
+        <v>3.81</v>
+      </c>
+      <c r="O86">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="P86">
+        <v>4.1719999999999997</v>
+      </c>
+      <c r="Q86">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>23</v>
+      </c>
+      <c r="B87" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87">
+        <v>16</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87">
+        <v>24</v>
+      </c>
+      <c r="G87">
+        <v>14</v>
+      </c>
+      <c r="H87">
+        <v>12</v>
+      </c>
+      <c r="I87">
+        <v>1026</v>
+      </c>
+      <c r="J87">
+        <v>295</v>
+      </c>
+      <c r="K87">
+        <v>56.600999999999999</v>
+      </c>
+      <c r="L87">
+        <v>11.327</v>
+      </c>
+      <c r="M87">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="N87">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="O87">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="P87">
+        <v>4.7380000000000004</v>
+      </c>
+      <c r="Q87">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>23</v>
+      </c>
+      <c r="B88" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88">
+        <v>16</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88">
+        <v>24</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>12</v>
+      </c>
+      <c r="I88">
+        <v>1091</v>
+      </c>
+      <c r="J88">
+        <v>715.6</v>
+      </c>
+      <c r="K88">
+        <v>59.408000000000001</v>
+      </c>
+      <c r="L88">
+        <v>8.5990000000000002</v>
+      </c>
+      <c r="M88">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="N88">
+        <v>1.66</v>
+      </c>
+      <c r="O88">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="P88">
+        <v>2.7480000000000002</v>
+      </c>
+      <c r="Q88">
+        <v>8.8999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89">
+        <v>16</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89" t="s">
+        <v>22</v>
+      </c>
+      <c r="F89">
+        <v>24</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>12</v>
+      </c>
+      <c r="I89">
+        <v>1098</v>
+      </c>
+      <c r="J89">
+        <v>714.1</v>
+      </c>
+      <c r="K89">
+        <v>59.48</v>
+      </c>
+      <c r="L89">
+        <v>8.7880000000000003</v>
+      </c>
+      <c r="M89">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="N89">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="O89">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="P89">
+        <v>1.1359999999999999</v>
+      </c>
+      <c r="Q89">
+        <v>7.8E-2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="11" orientation="portrait"/>
 </worksheet>
 </file>